--- a/examples/sequence/Cheeseboard/result/circle-1cm/no_tol/result.xlsx
+++ b/examples/sequence/Cheeseboard/result/circle-1cm/no_tol/result.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="find_reward" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="probe" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -69,6 +70,34 @@
       <left style="thin"/>
       <right style="thin"/>
       <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -496,181 +525,181 @@
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.63333333333333</v>
+        <v>57.04444444444444</v>
       </c>
       <c r="D3" t="n">
-        <v>0.025</v>
+        <v>0.9833333333333334</v>
       </c>
       <c r="E3" t="n">
-        <v>3.274602300723061</v>
+        <v>6.361311971063138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
       <c r="B4" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>42.96666666666666</v>
+      </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.602632801528086</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>56.75</v>
+      </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>1.058333333333333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.281976788810535</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>29.7</v>
+      </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.195173111769932</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>32.91666666666667</v>
+      </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.910535260297895</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>57.04444444444444</v>
+        <v>59.01666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9833333333333334</v>
+        <v>1.075</v>
       </c>
       <c r="E8" t="n">
-        <v>6.361311971063138</v>
+        <v>10.72048695328991</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.96666666666666</v>
+        <v>55.93333333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7416666666666667</v>
+        <v>1.308333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>4.602632801528086</v>
+        <v>12.80020809581548</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.75</v>
+        <v>21.43333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>1.058333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E10" t="n">
-        <v>9.281976788810535</v>
+        <v>4.460416455569415</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>29.7</v>
+        <v>34.63333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.025</v>
       </c>
       <c r="E11" t="n">
-        <v>7.195173111769932</v>
+        <v>3.274602300723061</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" t="n">
-        <v>32.91666666666667</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="E12" t="n">
-        <v>9.910535260297895</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" t="n">
-        <v>59.01666666666667</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>1.075</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10.72048695328991</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55.93333333333333</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>1.308333333333333</v>
-      </c>
-      <c r="E14" t="n">
-        <v>12.80020809581548</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C15" t="n">
-        <v>21.43333333333333</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6333333333333333</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4.460416455569415</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -692,189 +721,189 @@
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>16.33333333333333</v>
+        <v>52.2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2.596679098613295</v>
+        <v>9.18601214360897</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>35.47777777777777</v>
+      </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>1.116666666666667</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.34301299967117</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="1" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>33.03333333333333</v>
+        <v>18.91666666666667</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1416666666666667</v>
+        <v>2.575</v>
       </c>
       <c r="E19" t="n">
-        <v>4.339753530433999</v>
+        <v>2.545608699994898</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>43.46666666666667</v>
+        <v>42.3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.9</v>
       </c>
       <c r="E20" t="n">
-        <v>5.289852744637834</v>
+        <v>9.257742459591535</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>16.77777777777778</v>
+      </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>2.133333333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.089173498185293</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>52.2</v>
+        <v>12.7</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>9.18601214360897</v>
+        <v>1.428776249019339</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>35.47777777777777</v>
+        <v>19.15</v>
       </c>
       <c r="D23" t="n">
-        <v>1.116666666666667</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E23" t="n">
-        <v>6.34301299967117</v>
+        <v>3.434935243649924</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>18.91666666666667</v>
+        <v>67.93333333333334</v>
       </c>
       <c r="D24" t="n">
-        <v>2.575</v>
+        <v>1.325</v>
       </c>
       <c r="E24" t="n">
-        <v>2.545608699994898</v>
+        <v>13.9979529155149</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>42.3</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>9.257742459591535</v>
+        <v>2.596679098613295</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="n">
-        <v>16.77777777777778</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>2.133333333333333</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.089173498185293</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>12.7</v>
+        <v>33.03333333333333</v>
       </c>
       <c r="D27" t="n">
-        <v>1.333333333333333</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="E27" t="n">
-        <v>1.428776249019339</v>
+        <v>4.339753530433999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C28" t="n">
-        <v>19.15</v>
+        <v>43.46666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E28" t="n">
-        <v>3.434935243649924</v>
+        <v>5.289852744637834</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C29" t="n">
-        <v>67.93333333333334</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="E29" t="n">
-        <v>13.9979529155149</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -896,184 +925,184 @@
     <row r="31">
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>22.87777777777778</v>
+      </c>
       <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>1.558333333333333</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.366639601016784</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>63.16666666666666</v>
+      </c>
       <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
+        <v>1.275</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.284994056284894</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>43.41666666666666</v>
+      </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
+        <v>1.216666666666667</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.393770689681223</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>7.966666666666667</v>
+        <v>78.77499999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.9916666666666668</v>
       </c>
       <c r="E34" t="n">
-        <v>1.250022976910396</v>
+        <v>11.59782756715125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>7.633333333333334</v>
+        <v>18.25555555555555</v>
       </c>
       <c r="D35" t="n">
-        <v>0.15</v>
+        <v>2.511111111111111</v>
       </c>
       <c r="E35" t="n">
-        <v>5.456593316975515</v>
+        <v>3.292474765331684</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>22.87777777777778</v>
+        <v>64.35833333333333</v>
       </c>
       <c r="D36" t="n">
-        <v>1.558333333333333</v>
+        <v>0.8083333333333332</v>
       </c>
       <c r="E36" t="n">
-        <v>2.366639601016784</v>
+        <v>6.301327902555489</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>63.16666666666666</v>
+        <v>58.7</v>
       </c>
       <c r="D37" t="n">
-        <v>1.275</v>
+        <v>1.366666666666666</v>
       </c>
       <c r="E37" t="n">
-        <v>9.284994056284894</v>
+        <v>7.038880330391795</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C38" t="n">
-        <v>43.41666666666666</v>
+        <v>79.94166666666666</v>
       </c>
       <c r="D38" t="n">
-        <v>1.216666666666667</v>
+        <v>1.116666666666667</v>
       </c>
       <c r="E38" t="n">
-        <v>5.393770689681223</v>
+        <v>9.193532048120192</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="n">
-        <v>78.77499999999999</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>0.9916666666666668</v>
-      </c>
-      <c r="E39" t="n">
-        <v>11.59782756715125</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C40" t="n">
-        <v>18.25555555555555</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>2.511111111111111</v>
-      </c>
-      <c r="E40" t="n">
-        <v>3.292474765331684</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C41" t="n">
-        <v>64.35833333333333</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>0.8083333333333332</v>
-      </c>
-      <c r="E41" t="n">
-        <v>6.301327902555489</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C42" t="n">
-        <v>58.7</v>
+        <v>7.966666666666667</v>
       </c>
       <c r="D42" t="n">
-        <v>1.366666666666666</v>
+        <v>0.04444444444444445</v>
       </c>
       <c r="E42" t="n">
-        <v>7.038880330391795</v>
+        <v>1.250022976910396</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C43" t="n">
-        <v>79.94166666666666</v>
+        <v>7.633333333333334</v>
       </c>
       <c r="D43" t="n">
-        <v>1.116666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="E43" t="n">
-        <v>9.193532048120192</v>
+        <v>5.456593316975515</v>
       </c>
     </row>
     <row r="44">
@@ -1096,193 +1125,193 @@
     <row r="45">
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>6.866666666666666</v>
+        <v>16.30833333333333</v>
       </c>
       <c r="D45" t="n">
-        <v>0.03333333333333333</v>
+        <v>2.958333333333333</v>
       </c>
       <c r="E45" t="n">
-        <v>6.901144151431326</v>
+        <v>2.452255438205871</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>33.73333333333333</v>
+        <v>13.2</v>
       </c>
       <c r="D46" t="n">
-        <v>0.525</v>
+        <v>1.708333333333333</v>
       </c>
       <c r="E46" t="n">
-        <v>6.309211332731794</v>
+        <v>1.716493694782292</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>21.83333333333333</v>
+        <v>40.75</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1083333333333333</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="E47" t="n">
-        <v>2.291686997639065</v>
+        <v>4.533844480383401</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C48" t="n">
-        <v>10.86666666666667</v>
+        <v>12.94444444444444</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01111111111111111</v>
+        <v>1.783333333333333</v>
       </c>
       <c r="E48" t="n">
-        <v>1.453513695221256</v>
+        <v>2.225895176082948</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C49" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C49" t="n">
+        <v>27.98888888888889</v>
+      </c>
       <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
+        <v>3.355555555555556</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5.058851410858856</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>16.30833333333333</v>
+        <v>11.26666666666667</v>
       </c>
       <c r="D50" t="n">
-        <v>2.958333333333333</v>
+        <v>3.116666666666667</v>
       </c>
       <c r="E50" t="n">
-        <v>2.452255438205871</v>
+        <v>1.366462706458822</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>13.2</v>
+        <v>67.93333333333332</v>
       </c>
       <c r="D51" t="n">
-        <v>1.708333333333333</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="E51" t="n">
-        <v>1.716493694782292</v>
+        <v>8.461807430807237</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>40.75</v>
+        <v>27.47777777777778</v>
       </c>
       <c r="D52" t="n">
-        <v>1.466666666666667</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="E52" t="n">
-        <v>4.533844480383401</v>
+        <v>9.521657911573945</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>12.94444444444444</v>
+        <v>6.866666666666666</v>
       </c>
       <c r="D53" t="n">
-        <v>1.783333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E53" t="n">
-        <v>2.225895176082948</v>
+        <v>6.901144151431326</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>27.98888888888889</v>
+        <v>33.73333333333333</v>
       </c>
       <c r="D54" t="n">
-        <v>3.355555555555556</v>
+        <v>0.525</v>
       </c>
       <c r="E54" t="n">
-        <v>5.058851410858856</v>
+        <v>6.309211332731794</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C55" t="n">
-        <v>11.26666666666667</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="D55" t="n">
-        <v>3.116666666666667</v>
+        <v>0.1083333333333333</v>
       </c>
       <c r="E55" t="n">
-        <v>1.366462706458822</v>
+        <v>2.291686997639065</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C56" t="n">
-        <v>67.93333333333332</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="D56" t="n">
-        <v>1.466666666666667</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="E56" t="n">
-        <v>8.461807430807237</v>
+        <v>1.453513695221256</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C57" t="n">
-        <v>27.47777777777778</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>0.8833333333333333</v>
-      </c>
-      <c r="E57" t="n">
-        <v>9.521657911573945</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -1304,189 +1333,189 @@
     <row r="59">
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>22.4</v>
+        <v>11.3</v>
       </c>
       <c r="D59" t="n">
-        <v>0.008333333333333333</v>
+        <v>2.925</v>
       </c>
       <c r="E59" t="n">
-        <v>7.513680021435579</v>
+        <v>1.666639703290552</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>41.73333333333333</v>
+        <v>7.977777777777778</v>
       </c>
       <c r="D60" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="E60" t="n">
-        <v>4.122544585395568</v>
+        <v>1.011961193192788</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>6.866666666666666</v>
+        <v>15.68333333333333</v>
       </c>
       <c r="D61" t="n">
-        <v>0.01666666666666667</v>
+        <v>2.358333333333333</v>
       </c>
       <c r="E61" t="n">
-        <v>0.891370867297588</v>
+        <v>1.734202354299325</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C62" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C62" t="n">
+        <v>11.73333333333333</v>
+      </c>
       <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>2.533333333333333</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.672266825653427</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C63" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C63" t="n">
+        <v>50</v>
+      </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>2.155555555555555</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9.064373213782394</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C64" t="n">
-        <v>11.3</v>
+        <v>24.88333333333333</v>
       </c>
       <c r="D64" t="n">
-        <v>2.925</v>
+        <v>2.533333333333333</v>
       </c>
       <c r="E64" t="n">
-        <v>1.666639703290552</v>
+        <v>3.274549805514457</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C65" t="n">
-        <v>7.977777777777778</v>
+        <v>63.48333333333333</v>
       </c>
       <c r="D65" t="n">
-        <v>0.875</v>
+        <v>1.941666666666667</v>
       </c>
       <c r="E65" t="n">
-        <v>1.011961193192788</v>
+        <v>9.022320499766668</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C66" t="n">
-        <v>15.68333333333333</v>
+        <v>42.97777777777778</v>
       </c>
       <c r="D66" t="n">
-        <v>2.358333333333333</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="E66" t="n">
-        <v>1.734202354299325</v>
+        <v>11.94257983178418</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C67" t="n">
-        <v>11.73333333333333</v>
+        <v>22.4</v>
       </c>
       <c r="D67" t="n">
-        <v>2.533333333333333</v>
+        <v>0.008333333333333333</v>
       </c>
       <c r="E67" t="n">
-        <v>1.672266825653427</v>
+        <v>7.513680021435579</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C68" t="n">
-        <v>50</v>
+        <v>41.73333333333333</v>
       </c>
       <c r="D68" t="n">
-        <v>2.155555555555555</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="E68" t="n">
-        <v>9.064373213782394</v>
+        <v>4.122544585395568</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C69" t="n">
-        <v>24.88333333333333</v>
+        <v>6.866666666666666</v>
       </c>
       <c r="D69" t="n">
-        <v>2.533333333333333</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="E69" t="n">
-        <v>3.274549805514457</v>
+        <v>0.891370867297588</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C70" t="n">
-        <v>63.48333333333333</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>1.941666666666667</v>
-      </c>
-      <c r="E70" t="n">
-        <v>9.022320499766668</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C71" t="n">
-        <v>42.97777777777778</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>0.7833333333333333</v>
-      </c>
-      <c r="E71" t="n">
-        <v>11.94257983178418</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -1508,185 +1537,185 @@
     <row r="73">
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>42.26666666666667</v>
+        <v>8.383333333333333</v>
       </c>
       <c r="D73" t="n">
-        <v>0.025</v>
+        <v>3.391666666666667</v>
       </c>
       <c r="E73" t="n">
-        <v>6.637916963356815</v>
+        <v>1.084304398502724</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>14.63333333333333</v>
+        <v>25.50833333333333</v>
       </c>
       <c r="D74" t="n">
-        <v>0.008333333333333333</v>
+        <v>2.175</v>
       </c>
       <c r="E74" t="n">
-        <v>1.510698106332931</v>
+        <v>4.417778547976367</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C75" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C75" t="n">
+        <v>15.925</v>
+      </c>
       <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
+        <v>2.158333333333333</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.679622860662851</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C76" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C76" t="n">
+        <v>21.8</v>
+      </c>
       <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>2.691666666666667</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4.439852320190097</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C77" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C77" t="n">
+        <v>10.5</v>
+      </c>
       <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+        <v>1.733333333333333</v>
+      </c>
+      <c r="E77" t="n">
+        <v>9.942533216991615</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C78" t="n">
-        <v>8.383333333333333</v>
+        <v>11</v>
       </c>
       <c r="D78" t="n">
-        <v>3.391666666666667</v>
+        <v>3.458333333333333</v>
       </c>
       <c r="E78" t="n">
-        <v>1.084304398502724</v>
+        <v>1.255942501179933</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C79" t="n">
-        <v>25.50833333333333</v>
+        <v>43.775</v>
       </c>
       <c r="D79" t="n">
-        <v>2.175</v>
+        <v>1.425</v>
       </c>
       <c r="E79" t="n">
-        <v>4.417778547976367</v>
+        <v>6.887156571832088</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C80" t="n">
-        <v>15.925</v>
+        <v>49.97499999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>2.158333333333333</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>1.679622860662851</v>
+        <v>7.910846942569986</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C81" t="n">
-        <v>21.8</v>
+        <v>42.26666666666667</v>
       </c>
       <c r="D81" t="n">
-        <v>2.691666666666667</v>
+        <v>0.025</v>
       </c>
       <c r="E81" t="n">
-        <v>4.439852320190097</v>
+        <v>6.637916963356815</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C82" t="n">
-        <v>10.5</v>
+        <v>14.63333333333333</v>
       </c>
       <c r="D82" t="n">
-        <v>1.733333333333333</v>
+        <v>0.008333333333333333</v>
       </c>
       <c r="E82" t="n">
-        <v>9.942533216991615</v>
+        <v>1.510698106332931</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C83" t="n">
-        <v>11</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>3.458333333333333</v>
-      </c>
-      <c r="E83" t="n">
-        <v>1.255942501179933</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C84" t="n">
-        <v>43.775</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>1.425</v>
-      </c>
-      <c r="E84" t="n">
-        <v>6.887156571832088</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C85" t="n">
-        <v>49.97499999999999</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>0.8250000000000001</v>
-      </c>
-      <c r="E85" t="n">
-        <v>7.910846942569986</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -1708,181 +1737,181 @@
     <row r="87">
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C87" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>35.55833333333334</v>
+      </c>
       <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>2.758333333333334</v>
+      </c>
+      <c r="E87" t="n">
+        <v>5.359901000013179</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C88" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C88" t="n">
+        <v>10.05</v>
+      </c>
       <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>3.066666666666666</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2.090797614299221</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>16</v>
+        <v>3.883333333333334</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.966666666666667</v>
       </c>
       <c r="E89" t="n">
-        <v>2.005587595099918</v>
+        <v>1.652831057863768</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C90" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C90" t="n">
+        <v>10.05833333333334</v>
+      </c>
       <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
+        <v>2.008333333333333</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3.143136926027348</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C91" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C91" t="n">
+        <v>14.32222222222222</v>
+      </c>
       <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
+        <v>2.477777777777778</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4.634189170584943</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C92" t="n">
-        <v>35.55833333333334</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="D92" t="n">
-        <v>2.758333333333334</v>
+        <v>1.216666666666667</v>
       </c>
       <c r="E92" t="n">
-        <v>5.359901000013179</v>
+        <v>14.76162032937233</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C93" t="n">
-        <v>10.05</v>
+        <v>7.35</v>
       </c>
       <c r="D93" t="n">
-        <v>3.066666666666666</v>
+        <v>2.325</v>
       </c>
       <c r="E93" t="n">
-        <v>2.090797614299221</v>
+        <v>1.962430271280248</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>3.883333333333334</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="D94" t="n">
-        <v>1.966666666666667</v>
+        <v>1.183333333333333</v>
       </c>
       <c r="E94" t="n">
-        <v>1.652831057863768</v>
+        <v>2.775904489035667</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C95" t="n">
-        <v>10.05833333333334</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>2.008333333333333</v>
-      </c>
-      <c r="E95" t="n">
-        <v>3.143136926027348</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C96" t="n">
-        <v>14.32222222222222</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>2.477777777777778</v>
-      </c>
-      <c r="E96" t="n">
-        <v>4.634189170584943</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C97" t="n">
-        <v>18.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="D97" t="n">
-        <v>1.216666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E97" t="n">
-        <v>14.76162032937233</v>
+        <v>2.005587595099918</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C98" t="n">
-        <v>7.35</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="E98" t="n">
-        <v>1.962430271280248</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C99" t="n">
-        <v>10.13333333333333</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>1.183333333333333</v>
-      </c>
-      <c r="E99" t="n">
-        <v>2.775904489035667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -1904,177 +1933,177 @@
     <row r="101">
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C101" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C101" t="n">
+        <v>41.28888888888889</v>
+      </c>
       <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="E101" t="n">
+        <v>6.964436668999862</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C102" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C102" t="n">
+        <v>18.64444444444445</v>
+      </c>
       <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
+        <v>0.7833333333333333</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3.429053088196836</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C103" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C103" t="n">
+        <v>10.25</v>
+      </c>
       <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="inlineStr"/>
+        <v>2.491666666666667</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2.221278440447037</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C104" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C104" t="n">
+        <v>9.916666666666668</v>
+      </c>
       <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
+        <v>2.891666666666667</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1.664615434168704</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C105" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C105" t="n">
+        <v>20.95555555555556</v>
+      </c>
       <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
+        <v>3.322222222222222</v>
+      </c>
+      <c r="E105" t="n">
+        <v>6.854066891522126</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n"/>
       <c r="B106" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C106" t="n">
-        <v>41.28888888888889</v>
+        <v>6.116666666666666</v>
       </c>
       <c r="D106" t="n">
-        <v>1.4</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="E106" t="n">
-        <v>6.964436668999862</v>
+        <v>1.105165233544844</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C107" t="n">
-        <v>18.64444444444445</v>
+        <v>16.76666666666667</v>
       </c>
       <c r="D107" t="n">
-        <v>0.7833333333333333</v>
+        <v>2.325</v>
       </c>
       <c r="E107" t="n">
-        <v>3.429053088196836</v>
+        <v>2.762921245540948</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C108" t="n">
-        <v>10.25</v>
+        <v>7.316666666666666</v>
       </c>
       <c r="D108" t="n">
-        <v>2.491666666666667</v>
+        <v>0.925</v>
       </c>
       <c r="E108" t="n">
-        <v>2.221278440447037</v>
+        <v>12.14752889869932</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C109" t="n">
-        <v>9.916666666666668</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>2.891666666666667</v>
-      </c>
-      <c r="E109" t="n">
-        <v>1.664615434168704</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C110" t="n">
-        <v>20.95555555555556</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>3.322222222222222</v>
-      </c>
-      <c r="E110" t="n">
-        <v>6.854066891522126</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C111" t="n">
-        <v>6.116666666666666</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>2.466666666666667</v>
-      </c>
-      <c r="E111" t="n">
-        <v>1.105165233544844</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n"/>
       <c r="B112" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C112" t="n">
-        <v>16.76666666666667</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="E112" t="n">
-        <v>2.762921245540948</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C113" t="n">
-        <v>7.316666666666666</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E113" t="n">
-        <v>12.14752889869932</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -2096,189 +2125,189 @@
     <row r="115">
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C115" t="n">
-        <v>27.51666666666667</v>
+        <v>14.71666666666667</v>
       </c>
       <c r="D115" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="E115" t="n">
-        <v>3.138067655597091</v>
+        <v>1.488737883733154</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C116" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C116" t="n">
+        <v>29.85</v>
+      </c>
       <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="inlineStr"/>
+        <v>1.608333333333333</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3.233491504515989</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>47.56666666666667</v>
+        <v>37.58333333333334</v>
       </c>
       <c r="D117" t="n">
-        <v>0.1</v>
+        <v>1.766666666666667</v>
       </c>
       <c r="E117" t="n">
-        <v>5.366395522496633</v>
+        <v>4.503501308725391</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C118" t="n">
-        <v>49.73333333333333</v>
+        <v>40.06666666666667</v>
       </c>
       <c r="D118" t="n">
-        <v>0.6444444444444445</v>
+        <v>3.616666666666667</v>
       </c>
       <c r="E118" t="n">
-        <v>4.295511063265473</v>
+        <v>9.712469613145258</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C119" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C119" t="n">
+        <v>40.44444444444445</v>
+      </c>
       <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="inlineStr"/>
+        <v>2.344444444444445</v>
+      </c>
+      <c r="E119" t="n">
+        <v>10.78414564497414</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n"/>
       <c r="B120" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C120" t="n">
-        <v>14.71666666666667</v>
+        <v>26.40833333333333</v>
       </c>
       <c r="D120" t="n">
-        <v>0.7333333333333334</v>
+        <v>2.6</v>
       </c>
       <c r="E120" t="n">
-        <v>1.488737883733154</v>
+        <v>10.54717772471813</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n"/>
       <c r="B121" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C121" t="n">
-        <v>29.85</v>
+        <v>56.98888888888889</v>
       </c>
       <c r="D121" t="n">
-        <v>1.608333333333333</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="E121" t="n">
-        <v>3.233491504515989</v>
+        <v>5.217390748021457</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n"/>
       <c r="B122" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C122" t="n">
-        <v>37.58333333333334</v>
+        <v>47.38333333333334</v>
       </c>
       <c r="D122" t="n">
-        <v>1.766666666666667</v>
+        <v>1.991666666666666</v>
       </c>
       <c r="E122" t="n">
-        <v>4.503501308725391</v>
+        <v>6.561920888163015</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n"/>
       <c r="B123" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C123" t="n">
-        <v>40.06666666666667</v>
+        <v>27.51666666666667</v>
       </c>
       <c r="D123" t="n">
-        <v>3.616666666666667</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E123" t="n">
-        <v>9.712469613145258</v>
+        <v>3.138067655597091</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n"/>
       <c r="B124" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C124" t="n">
-        <v>40.44444444444445</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>2.344444444444445</v>
-      </c>
-      <c r="E124" t="n">
-        <v>10.78414564497414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n"/>
       <c r="B125" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C125" t="n">
-        <v>26.40833333333333</v>
+        <v>47.56666666666667</v>
       </c>
       <c r="D125" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="E125" t="n">
-        <v>10.54717772471813</v>
+        <v>5.366395522496633</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n"/>
       <c r="B126" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C126" t="n">
-        <v>56.98888888888889</v>
+        <v>49.73333333333333</v>
       </c>
       <c r="D126" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="E126" t="n">
-        <v>5.217390748021457</v>
+        <v>4.295511063265473</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n"/>
       <c r="B127" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C127" t="n">
-        <v>47.38333333333334</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>1.991666666666666</v>
-      </c>
-      <c r="E127" t="n">
-        <v>6.561920888163015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -2300,181 +2329,181 @@
     <row r="129">
       <c r="A129" s="1" t="n"/>
       <c r="B129" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C129" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C129" t="n">
+        <v>18.61666666666667</v>
+      </c>
       <c r="D129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" t="inlineStr"/>
+        <v>1.775</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3.527158964389519</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n"/>
       <c r="B130" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
-        <v>-1.966666666666667</v>
+        <v>12.40833333333333</v>
       </c>
       <c r="D130" t="n">
-        <v>0.06666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>8.88870050737137</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n"/>
       <c r="B131" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C131" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C131" t="n">
+        <v>10.99166666666667</v>
+      </c>
       <c r="D131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" t="inlineStr"/>
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1.54529608343032</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n"/>
       <c r="B132" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C132" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C132" t="n">
+        <v>6.208333333333333</v>
+      </c>
       <c r="D132" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" t="inlineStr"/>
+        <v>2.108333333333333</v>
+      </c>
+      <c r="E132" t="n">
+        <v>4.646294393061982</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n"/>
       <c r="B133" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C133" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C133" t="n">
+        <v>8.422222222222222</v>
+      </c>
       <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="inlineStr"/>
+        <v>2.011111111111112</v>
+      </c>
+      <c r="E133" t="n">
+        <v>5.156501928879124</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n"/>
       <c r="B134" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C134" t="n">
-        <v>18.61666666666667</v>
+        <v>5.691666666666666</v>
       </c>
       <c r="D134" t="n">
-        <v>1.775</v>
+        <v>1.525</v>
       </c>
       <c r="E134" t="n">
-        <v>3.527158964389519</v>
+        <v>7.153245145917262</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n"/>
       <c r="B135" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C135" t="n">
-        <v>12.40833333333333</v>
+        <v>51.58333333333333</v>
       </c>
       <c r="D135" t="n">
-        <v>1.666666666666667</v>
+        <v>1.208333333333333</v>
       </c>
       <c r="E135" t="n">
-        <v>8.88870050737137</v>
+        <v>7.181902151089716</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n"/>
       <c r="B136" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C136" t="n">
-        <v>10.99166666666667</v>
+        <v>33.02222222222223</v>
       </c>
       <c r="D136" t="n">
-        <v>0.8833333333333333</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E136" t="n">
-        <v>1.54529608343032</v>
+        <v>8.568441848242822</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n"/>
       <c r="B137" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C137" t="n">
-        <v>6.208333333333333</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>2.108333333333333</v>
-      </c>
-      <c r="E137" t="n">
-        <v>4.646294393061982</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n"/>
       <c r="B138" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C138" t="n">
-        <v>8.422222222222222</v>
+        <v>-1.966666666666667</v>
       </c>
       <c r="D138" t="n">
-        <v>2.011111111111112</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E138" t="n">
-        <v>5.156501928879124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n"/>
       <c r="B139" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C139" t="n">
-        <v>5.691666666666666</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>1.525</v>
-      </c>
-      <c r="E139" t="n">
-        <v>7.153245145917262</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n"/>
       <c r="B140" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C140" t="n">
-        <v>51.58333333333333</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>1.208333333333333</v>
-      </c>
-      <c r="E140" t="n">
-        <v>7.181902151089716</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n"/>
       <c r="B141" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C141" t="n">
-        <v>33.02222222222223</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E141" t="n">
-        <v>8.568441848242822</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -2496,185 +2525,185 @@
     <row r="143">
       <c r="A143" s="1" t="n"/>
       <c r="B143" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C143" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C143" t="n">
+        <v>20.175</v>
+      </c>
       <c r="D143" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" t="inlineStr"/>
+        <v>3.133333333333333</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3.110488077677673</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n"/>
       <c r="B144" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C144" t="n">
-        <v>3.333333333333333</v>
+        <v>9.222222222222221</v>
       </c>
       <c r="D144" t="n">
-        <v>0.025</v>
+        <v>2.058333333333334</v>
       </c>
       <c r="E144" t="n">
-        <v>0.8288390176473027</v>
+        <v>1.440883272479521</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n"/>
       <c r="B145" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C145" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C145" t="n">
+        <v>7.741666666666667</v>
+      </c>
       <c r="D145" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" t="inlineStr"/>
+        <v>2.125</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2.780807725162335</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n"/>
       <c r="B146" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C146" t="n">
-        <v>6.266666666666667</v>
+        <v>12.89166666666667</v>
       </c>
       <c r="D146" t="n">
-        <v>0.02222222222222222</v>
+        <v>1.525</v>
       </c>
       <c r="E146" t="n">
-        <v>0.9909713829240201</v>
+        <v>1.992936042479869</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n"/>
       <c r="B147" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C147" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C147" t="n">
+        <v>20.85555555555556</v>
+      </c>
       <c r="D147" t="n">
-        <v>0</v>
-      </c>
-      <c r="E147" t="inlineStr"/>
+        <v>1.833333333333333</v>
+      </c>
+      <c r="E147" t="n">
+        <v>10.17451812470561</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n"/>
       <c r="B148" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C148" t="n">
-        <v>20.175</v>
+        <v>6.183333333333334</v>
       </c>
       <c r="D148" t="n">
-        <v>3.133333333333333</v>
+        <v>1.658333333333333</v>
       </c>
       <c r="E148" t="n">
-        <v>3.110488077677673</v>
+        <v>4.017471867456717</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n"/>
       <c r="B149" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C149" t="n">
-        <v>9.222222222222221</v>
+        <v>39.41666666666666</v>
       </c>
       <c r="D149" t="n">
-        <v>2.058333333333334</v>
+        <v>2.075</v>
       </c>
       <c r="E149" t="n">
-        <v>1.440883272479521</v>
+        <v>8.929617329368492</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n"/>
       <c r="B150" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C150" t="n">
-        <v>7.741666666666667</v>
+        <v>16.24166666666667</v>
       </c>
       <c r="D150" t="n">
-        <v>2.125</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E150" t="n">
-        <v>2.780807725162335</v>
+        <v>3.342964286875895</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n"/>
       <c r="B151" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C151" t="n">
-        <v>12.89166666666667</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>1.525</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1.992936042479869</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n"/>
       <c r="B152" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C152" t="n">
-        <v>20.85555555555556</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D152" t="n">
-        <v>1.833333333333333</v>
+        <v>0.025</v>
       </c>
       <c r="E152" t="n">
-        <v>10.17451812470561</v>
+        <v>0.8288390176473027</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n"/>
       <c r="B153" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C153" t="n">
-        <v>6.183333333333334</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>1.658333333333333</v>
-      </c>
-      <c r="E153" t="n">
-        <v>4.017471867456717</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n"/>
       <c r="B154" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C154" t="n">
-        <v>39.41666666666666</v>
+        <v>6.266666666666667</v>
       </c>
       <c r="D154" t="n">
-        <v>2.075</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E154" t="n">
-        <v>8.929617329368492</v>
+        <v>0.9909713829240201</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n"/>
       <c r="B155" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C155" t="n">
-        <v>16.24166666666667</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="E155" t="n">
-        <v>3.342964286875895</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -2696,184 +2725,184 @@
     <row r="157">
       <c r="A157" s="1" t="n"/>
       <c r="B157" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C157" t="n">
-        <v>14.56666666666667</v>
+        <v>35.40000000000001</v>
       </c>
       <c r="D157" t="n">
-        <v>0.04166666666666666</v>
+        <v>1.1</v>
       </c>
       <c r="E157" t="n">
-        <v>1.831092312823296</v>
+        <v>3.884257583799182</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n"/>
       <c r="B158" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C158" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C158" t="n">
+        <v>17.3</v>
+      </c>
       <c r="D158" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" t="inlineStr"/>
+        <v>2.375</v>
+      </c>
+      <c r="E158" t="n">
+        <v>3.897619306136435</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n"/>
       <c r="B159" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C159" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C159" t="n">
+        <v>49.38333333333333</v>
+      </c>
       <c r="D159" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="E159" t="n">
+        <v>13.34668752490294</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n"/>
       <c r="B160" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C160" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C160" t="n">
+        <v>27.2</v>
+      </c>
       <c r="D160" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" t="inlineStr"/>
+        <v>2.591666666666667</v>
+      </c>
+      <c r="E160" t="n">
+        <v>9.750966809166925</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n"/>
       <c r="B161" s="1" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C161" t="n">
-        <v>-2.133333333333333</v>
+        <v>26.01111111111111</v>
       </c>
       <c r="D161" t="n">
-        <v>0.04166666666666666</v>
+        <v>1.944444444444444</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>3.460552256500861</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n"/>
       <c r="B162" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C162" t="n">
-        <v>35.40000000000001</v>
+        <v>47.59166666666667</v>
       </c>
       <c r="D162" t="n">
-        <v>1.1</v>
+        <v>1.625</v>
       </c>
       <c r="E162" t="n">
-        <v>3.884257583799182</v>
+        <v>5.327965495113151</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n"/>
       <c r="B163" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C163" t="n">
-        <v>17.3</v>
+        <v>31.86666666666667</v>
       </c>
       <c r="D163" t="n">
-        <v>2.375</v>
+        <v>1.575</v>
       </c>
       <c r="E163" t="n">
-        <v>3.897619306136435</v>
+        <v>10.19893414722147</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n"/>
       <c r="B164" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C164" t="n">
-        <v>49.38333333333333</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="D164" t="n">
-        <v>2.4</v>
+        <v>1.425</v>
       </c>
       <c r="E164" t="n">
-        <v>13.34668752490294</v>
+        <v>3.488864381204042</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n"/>
       <c r="B165" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C165" t="n">
-        <v>27.2</v>
+        <v>14.56666666666667</v>
       </c>
       <c r="D165" t="n">
-        <v>2.591666666666667</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="E165" t="n">
-        <v>9.750966809166925</v>
+        <v>1.831092312823296</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n"/>
       <c r="B166" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C166" t="n">
-        <v>26.01111111111111</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>1.944444444444444</v>
-      </c>
-      <c r="E166" t="n">
-        <v>3.460552256500861</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n"/>
       <c r="B167" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C167" t="n">
-        <v>47.59166666666667</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="E167" t="n">
-        <v>5.327965495113151</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n"/>
       <c r="B168" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C168" t="n">
-        <v>31.86666666666667</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>1.575</v>
-      </c>
-      <c r="E168" t="n">
-        <v>10.19893414722147</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n"/>
       <c r="B169" s="1" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C169" t="n">
-        <v>24.33333333333333</v>
+        <v>-2.133333333333333</v>
       </c>
       <c r="D169" t="n">
-        <v>1.425</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="E169" t="n">
-        <v>3.488864381204042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -2896,185 +2925,185 @@
     <row r="171">
       <c r="A171" s="1" t="n"/>
       <c r="B171" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C171" t="n">
-        <v>23.03333333333333</v>
+        <v>40.59999999999999</v>
       </c>
       <c r="D171" t="n">
-        <v>0.04166666666666667</v>
+        <v>2.008333333333333</v>
       </c>
       <c r="E171" t="n">
-        <v>2.642373780505995</v>
+        <v>4.978528475295672</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n"/>
       <c r="B172" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C172" t="n">
-        <v>63.96666666666667</v>
+        <v>29.8</v>
       </c>
       <c r="D172" t="n">
-        <v>0.01666666666666667</v>
+        <v>1.391666666666667</v>
       </c>
       <c r="E172" t="n">
-        <v>6.193280775913687</v>
+        <v>3.240292271561215</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n"/>
       <c r="B173" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C173" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C173" t="n">
+        <v>28.92222222222223</v>
+      </c>
       <c r="D173" t="n">
-        <v>0</v>
-      </c>
-      <c r="E173" t="inlineStr"/>
+        <v>1.691666666666667</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2.887706499715934</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n"/>
       <c r="B174" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C174" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C174" t="n">
+        <v>16.3</v>
+      </c>
       <c r="D174" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="E174" t="n">
+        <v>2.380692966955412</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n"/>
       <c r="B175" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C175" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C175" t="n">
+        <v>71.34999999999999</v>
+      </c>
       <c r="D175" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" t="inlineStr"/>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="E175" t="n">
+        <v>10.62651692502825</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n"/>
       <c r="B176" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C176" t="n">
-        <v>40.59999999999999</v>
+        <v>71.81111111111112</v>
       </c>
       <c r="D176" t="n">
-        <v>2.008333333333333</v>
+        <v>1.65</v>
       </c>
       <c r="E176" t="n">
-        <v>4.978528475295672</v>
+        <v>13.07021234131527</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n"/>
       <c r="B177" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C177" t="n">
-        <v>29.8</v>
+        <v>14.05833333333333</v>
       </c>
       <c r="D177" t="n">
-        <v>1.391666666666667</v>
+        <v>2.408333333333333</v>
       </c>
       <c r="E177" t="n">
-        <v>3.240292271561215</v>
+        <v>6.112319413367288</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n"/>
       <c r="B178" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C178" t="n">
-        <v>28.92222222222223</v>
+        <v>62.00833333333333</v>
       </c>
       <c r="D178" t="n">
-        <v>1.691666666666667</v>
+        <v>1.425</v>
       </c>
       <c r="E178" t="n">
-        <v>2.887706499715934</v>
+        <v>8.080480172680272</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n"/>
       <c r="B179" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C179" t="n">
-        <v>16.3</v>
+        <v>23.03333333333333</v>
       </c>
       <c r="D179" t="n">
-        <v>2.75</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="E179" t="n">
-        <v>2.380692966955412</v>
+        <v>2.642373780505995</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n"/>
       <c r="B180" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C180" t="n">
-        <v>71.34999999999999</v>
+        <v>63.96666666666667</v>
       </c>
       <c r="D180" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="E180" t="n">
-        <v>10.62651692502825</v>
+        <v>6.193280775913687</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n"/>
       <c r="B181" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C181" t="n">
-        <v>71.81111111111112</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E181" t="n">
-        <v>13.07021234131527</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n"/>
       <c r="B182" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C182" t="n">
-        <v>14.05833333333333</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>2.408333333333333</v>
-      </c>
-      <c r="E182" t="n">
-        <v>6.112319413367288</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n"/>
       <c r="B183" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C183" t="n">
-        <v>62.00833333333333</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>1.425</v>
-      </c>
-      <c r="E183" t="n">
-        <v>8.080480172680272</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -3096,188 +3125,188 @@
     <row r="185">
       <c r="A185" s="1" t="n"/>
       <c r="B185" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C185" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C185" t="n">
+        <v>8.216666666666667</v>
+      </c>
       <c r="D185" t="n">
-        <v>0</v>
-      </c>
-      <c r="E185" t="inlineStr"/>
+        <v>1.525</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1.530945378460471</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n"/>
       <c r="B186" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C186" t="n">
-        <v>2.2</v>
+        <v>11.89166666666667</v>
       </c>
       <c r="D186" t="n">
-        <v>0.04166666666666667</v>
+        <v>2.516666666666667</v>
       </c>
       <c r="E186" t="n">
-        <v>0.6039102835410687</v>
+        <v>2.59987892000141</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n"/>
       <c r="B187" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C187" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C187" t="n">
+        <v>3.433333333333334</v>
+      </c>
       <c r="D187" t="n">
-        <v>0</v>
-      </c>
-      <c r="E187" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.9332759532196953</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n"/>
       <c r="B188" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C188" t="n">
-        <v>7.15</v>
+        <v>2.825</v>
       </c>
       <c r="D188" t="n">
-        <v>0.03333333333333333</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="E188" t="n">
-        <v>1.232280553106597</v>
+        <v>0.6354325436321091</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n"/>
       <c r="B189" s="1" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C189" t="n">
-        <v>3.9</v>
+        <v>7.944444444444444</v>
       </c>
       <c r="D189" t="n">
-        <v>0.01666666666666667</v>
+        <v>1.933333333333333</v>
       </c>
       <c r="E189" t="n">
-        <v>0.8020285580380152</v>
+        <v>10.70841730390438</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n"/>
       <c r="B190" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C190" t="n">
-        <v>8.216666666666667</v>
+        <v>5.683333333333334</v>
       </c>
       <c r="D190" t="n">
-        <v>1.525</v>
+        <v>1.441666666666667</v>
       </c>
       <c r="E190" t="n">
-        <v>1.530945378460471</v>
+        <v>10.65607320234036</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n"/>
       <c r="B191" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C191" t="n">
-        <v>11.89166666666667</v>
+        <v>9.308333333333334</v>
       </c>
       <c r="D191" t="n">
-        <v>2.516666666666667</v>
+        <v>2.541666666666667</v>
       </c>
       <c r="E191" t="n">
-        <v>2.59987892000141</v>
+        <v>11.56688255606696</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n"/>
       <c r="B192" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C192" t="n">
-        <v>3.433333333333334</v>
+        <v>9.908333333333333</v>
       </c>
       <c r="D192" t="n">
-        <v>2.4</v>
+        <v>1.708333333333333</v>
       </c>
       <c r="E192" t="n">
-        <v>0.9332759532196953</v>
+        <v>1.771712324616401</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n"/>
       <c r="B193" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C193" t="n">
-        <v>2.825</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="E193" t="n">
-        <v>0.6354325436321091</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n"/>
       <c r="B194" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C194" t="n">
-        <v>7.944444444444444</v>
+        <v>2.2</v>
       </c>
       <c r="D194" t="n">
-        <v>1.933333333333333</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="E194" t="n">
-        <v>10.70841730390438</v>
+        <v>0.6039102835410687</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n"/>
       <c r="B195" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C195" t="n">
-        <v>5.683333333333334</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
-        <v>1.441666666666667</v>
-      </c>
-      <c r="E195" t="n">
-        <v>10.65607320234036</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n"/>
       <c r="B196" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C196" t="n">
-        <v>9.308333333333334</v>
+        <v>7.15</v>
       </c>
       <c r="D196" t="n">
-        <v>2.541666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E196" t="n">
-        <v>11.56688255606696</v>
+        <v>1.232280553106597</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n"/>
       <c r="B197" s="1" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C197" t="n">
-        <v>9.908333333333333</v>
+        <v>3.9</v>
       </c>
       <c r="D197" t="n">
-        <v>1.708333333333333</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="E197" t="n">
-        <v>1.771712324616401</v>
+        <v>0.8020285580380152</v>
       </c>
     </row>
     <row r="198">
@@ -3300,177 +3329,177 @@
     <row r="199">
       <c r="A199" s="1" t="n"/>
       <c r="B199" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C199" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C199" t="n">
+        <v>20.94444444444444</v>
+      </c>
       <c r="D199" t="n">
-        <v>0</v>
-      </c>
-      <c r="E199" t="inlineStr"/>
+        <v>2.558333333333333</v>
+      </c>
+      <c r="E199" t="n">
+        <v>4.243493985969068</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n"/>
       <c r="B200" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C200" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C200" t="n">
+        <v>70.2</v>
+      </c>
       <c r="D200" t="n">
-        <v>0</v>
-      </c>
-      <c r="E200" t="inlineStr"/>
+        <v>2.616666666666667</v>
+      </c>
+      <c r="E200" t="n">
+        <v>6.255424834249827</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n"/>
       <c r="B201" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C201" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C201" t="n">
+        <v>21.5</v>
+      </c>
       <c r="D201" t="n">
-        <v>0</v>
-      </c>
-      <c r="E201" t="inlineStr"/>
+        <v>3.016666666666667</v>
+      </c>
+      <c r="E201" t="n">
+        <v>5.68480735714112</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n"/>
       <c r="B202" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C202" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C202" t="n">
+        <v>26.8</v>
+      </c>
       <c r="D202" t="n">
-        <v>0</v>
-      </c>
-      <c r="E202" t="inlineStr"/>
+        <v>2.716666666666667</v>
+      </c>
+      <c r="E202" t="n">
+        <v>9.301115845918229</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n"/>
       <c r="B203" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C203" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C203" t="n">
+        <v>18.52222222222222</v>
+      </c>
       <c r="D203" t="n">
-        <v>0</v>
-      </c>
-      <c r="E203" t="inlineStr"/>
+        <v>2.488888888888889</v>
+      </c>
+      <c r="E203" t="n">
+        <v>9.707485367478929</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n"/>
       <c r="B204" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C204" t="n">
-        <v>20.94444444444444</v>
+        <v>15.88333333333333</v>
       </c>
       <c r="D204" t="n">
-        <v>2.558333333333333</v>
+        <v>3.008333333333334</v>
       </c>
       <c r="E204" t="n">
-        <v>4.243493985969068</v>
+        <v>14.46564056052877</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n"/>
       <c r="B205" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C205" t="n">
-        <v>70.2</v>
+        <v>48.31666666666666</v>
       </c>
       <c r="D205" t="n">
-        <v>2.616666666666667</v>
+        <v>2.016666666666667</v>
       </c>
       <c r="E205" t="n">
-        <v>6.255424834249827</v>
+        <v>5.38868768572926</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n"/>
       <c r="B206" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C206" t="n">
-        <v>21.5</v>
+        <v>61.03333333333333</v>
       </c>
       <c r="D206" t="n">
-        <v>3.016666666666667</v>
+        <v>1.808333333333333</v>
       </c>
       <c r="E206" t="n">
-        <v>5.68480735714112</v>
+        <v>9.956007452739735</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n"/>
       <c r="B207" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C207" t="n">
-        <v>26.8</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>2.716666666666667</v>
-      </c>
-      <c r="E207" t="n">
-        <v>9.301115845918229</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n"/>
       <c r="B208" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C208" t="n">
-        <v>18.52222222222222</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
-        <v>2.488888888888889</v>
-      </c>
-      <c r="E208" t="n">
-        <v>9.707485367478929</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n"/>
       <c r="B209" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C209" t="n">
-        <v>15.88333333333333</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>3.008333333333334</v>
-      </c>
-      <c r="E209" t="n">
-        <v>14.46564056052877</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n"/>
       <c r="B210" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C210" t="n">
-        <v>48.31666666666666</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>2.016666666666667</v>
-      </c>
-      <c r="E210" t="n">
-        <v>5.38868768572926</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n"/>
       <c r="B211" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C211" t="n">
-        <v>61.03333333333333</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>1.808333333333333</v>
-      </c>
-      <c r="E211" t="n">
-        <v>9.956007452739735</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -3492,185 +3521,185 @@
     <row r="213">
       <c r="A213" s="1" t="n"/>
       <c r="B213" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C213" t="n">
-        <v>34.9</v>
+        <v>25.52222222222222</v>
       </c>
       <c r="D213" t="n">
-        <v>0.04166666666666666</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="E213" t="n">
-        <v>3.269082177268933</v>
+        <v>3.595061811319953</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n"/>
       <c r="B214" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C214" t="n">
-        <v>43.86666666666667</v>
+        <v>32.975</v>
       </c>
       <c r="D214" t="n">
-        <v>0.025</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="E214" t="n">
-        <v>3.79528941125802</v>
+        <v>4.81509041987014</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n"/>
       <c r="B215" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C215" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C215" t="n">
+        <v>45.5</v>
+      </c>
       <c r="D215" t="n">
-        <v>0</v>
-      </c>
-      <c r="E215" t="inlineStr"/>
+        <v>2.216666666666667</v>
+      </c>
+      <c r="E215" t="n">
+        <v>5.768930441403339</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n"/>
       <c r="B216" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C216" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C216" t="n">
+        <v>17.14166666666667</v>
+      </c>
       <c r="D216" t="n">
-        <v>0</v>
-      </c>
-      <c r="E216" t="inlineStr"/>
+        <v>2.2</v>
+      </c>
+      <c r="E216" t="n">
+        <v>7.391816670594023</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n"/>
       <c r="B217" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C217" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C217" t="n">
+        <v>48.97777777777777</v>
+      </c>
       <c r="D217" t="n">
-        <v>0</v>
-      </c>
-      <c r="E217" t="inlineStr"/>
+        <v>3.133333333333333</v>
+      </c>
+      <c r="E217" t="n">
+        <v>9.839545694659812</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n"/>
       <c r="B218" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C218" t="n">
-        <v>25.52222222222222</v>
+        <v>65.925</v>
       </c>
       <c r="D218" t="n">
-        <v>1.583333333333333</v>
+        <v>1.966666666666667</v>
       </c>
       <c r="E218" t="n">
-        <v>3.595061811319953</v>
+        <v>7.137886594739153</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n"/>
       <c r="B219" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C219" t="n">
-        <v>32.975</v>
+        <v>50.14166666666667</v>
       </c>
       <c r="D219" t="n">
-        <v>2.233333333333333</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="E219" t="n">
-        <v>4.81509041987014</v>
+        <v>9.844593384109865</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n"/>
       <c r="B220" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C220" t="n">
-        <v>45.5</v>
+        <v>54.88333333333334</v>
       </c>
       <c r="D220" t="n">
-        <v>2.216666666666667</v>
+        <v>1.2</v>
       </c>
       <c r="E220" t="n">
-        <v>5.768930441403339</v>
+        <v>10.05997198829834</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n"/>
       <c r="B221" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C221" t="n">
-        <v>17.14166666666667</v>
+        <v>34.9</v>
       </c>
       <c r="D221" t="n">
-        <v>2.2</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="E221" t="n">
-        <v>7.391816670594023</v>
+        <v>3.269082177268933</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n"/>
       <c r="B222" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C222" t="n">
-        <v>48.97777777777777</v>
+        <v>43.86666666666667</v>
       </c>
       <c r="D222" t="n">
-        <v>3.133333333333333</v>
+        <v>0.025</v>
       </c>
       <c r="E222" t="n">
-        <v>9.839545694659812</v>
+        <v>3.79528941125802</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n"/>
       <c r="B223" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C223" t="n">
-        <v>65.925</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
-        <v>1.966666666666667</v>
-      </c>
-      <c r="E223" t="n">
-        <v>7.137886594739153</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n"/>
       <c r="B224" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C224" t="n">
-        <v>50.14166666666667</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>0.3416666666666667</v>
-      </c>
-      <c r="E224" t="n">
-        <v>9.844593384109865</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n"/>
       <c r="B225" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C225" t="n">
-        <v>54.88333333333334</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E225" t="n">
-        <v>10.05997198829834</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3693,4 +3722,1287 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cheeseboard</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>StartToReward</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>RewardAreaSeconds</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>RewardTraceSeconds</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Displacement</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>MedianSpeed</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>MedianAcceleration</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>FreezingTime</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Displacement</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>MedianSpeed</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>MedianAcceleration</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>FreezingTime</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Animal</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>392</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D4" t="n">
+        <v>23.13333333333333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.001151537856714</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.08523078021641828</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03614988714341139</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16.32111530398465</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.07493296597645493</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02464222674425157</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>31.47961725836925</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.08728887520518247</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03543844898661075</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>393</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2.266666666666667</v>
+      </c>
+      <c r="D6" t="n">
+        <v>89.16666666666667</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.48349130473277</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0881404042752334</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03747132920588458</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24.69947539959005</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0869949848202799</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.03380416309397682</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="D7" t="n">
+        <v>31.23333333333333</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.86154873564778</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1394481646430769</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.07220063059288762</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>35.97127663624696</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1179770250263837</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.05559128964597632</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>401</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="D8" t="n">
+        <v>92.36666666666666</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.604136536628446</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03837318380892585</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02091136010899158</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>14.45236511395824</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.04399064207420716</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01978526240977097</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="D9" t="n">
+        <v>95.63333333333334</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.97686487025571</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.100335762394547</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.03549649575382685</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>35.0785280389782</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1152320800327817</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.04050387861306612</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>402</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>41.76666666666667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.742570428929052</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.07336951396049485</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.03508186777501887</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14.26950355444411</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.06147500326727118</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02934849624445274</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>29.91368854831759</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0926486584844497</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.04366213999407262</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>403</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>90.96666666666667</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18.33410795195148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1242561154499587</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.04793020149743007</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23.06156902924873</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1219565359242782</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.050363236040048</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>31.13063417843095</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.08532424168929253</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.05256407531570809</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>407</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18.37711663597987</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0833225227403375</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.03515719116196631</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>21.85865566136449</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.06998545704896242</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02605537535101499</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>30.45686380818719</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1249691925464514</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.05677834928303305</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>411</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="D16" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.45475266743955</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1424987858633802</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.08424275789726265</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>27.95939493045646</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1370839999895902</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.05414003977217663</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="D17" t="n">
+        <v>26.03333333333333</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.807726601004582</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1030536447352629</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05513988031541517</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>29.81096294274179</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1297016632141802</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.05736888767172402</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>413</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8.287891781727025</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1896536906935271</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.118740328079743</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>30.10490716460016</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.1195839609686221</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.05996357322682117</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.033333333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.633333333333334</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9665277224259079</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1512964333095431</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.04765530234579718</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>25.65657395441917</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1151456090223114</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0473945041846254</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>443</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="D20" t="n">
+        <v>37.03333333333333</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8.129445368564197</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.07328306380142702</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.03447907963461977</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15.13229864992659</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.07048741289445043</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.02463606078471703</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6.966666666666667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9840577576844389</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1273652033873545</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05502292610233944</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>36.33449286672786</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0852288950086732</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0380074687680782</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>444</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>15.77598614771186</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.0783903304630616</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.04932199590756003</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.066666666666667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5538464842103791</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.2699191452829783</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1420566712420309</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>36.70694567820345</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.1263110213545617</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.04846293949391389</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>445</v>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>21.21991340886674</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1396504075381272</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.07619440434722613</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7.033333333333333</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.795172084896729</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.2490663820294633</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.08395430555900785</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>35.80783684033896</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.1714786377117012</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.07235111319115478</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>448</v>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.907732454643674</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.09066456888638647</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.03384101249901839</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>14.87437057718662</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.08796987792223548</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.02839834001475894</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>61.66666666666666</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10.3906407310753</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.1128671830617047</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.04071287832037901</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>29.24868478753031</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.1256293144111004</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.0458469068325047</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>454</v>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="D28" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.987095744623251</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.09147816587111068</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.03411756001047819</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>11.03427134437203</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.07907660258703014</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.02926750256183636</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>32.44442802535801</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.07644651173665584</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.03414048398171043</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>461</v>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>12.29494609105018</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1988263908801756</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05432115927238113</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>29.88439970994561</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.1804350833940791</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.08373274131401742</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="D31" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>13.92874562084311</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1450421747622433</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.04682115908382689</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>34.73620624641121</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.1374070785219114</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.06283871444370703</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>463</v>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>20.03333333333333</v>
+      </c>
+      <c r="E32" t="n">
+        <v>13.44476869600894</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2071050464209356</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1371619240784181</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>23.21923990196483</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.1119666023320491</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.05458001948237035</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>18.01824454951548</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.05863040516997148</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.02799943723033593</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>465</v>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>21.43333333333333</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.81331259301124</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.1865012600798798</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.087389004308291</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>26.13435435376287</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.1244851065357632</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.06375015830778874</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>25.70428752628436</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.08816934478412819</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.03236613955332235</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>